--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.008138815107534114</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.03280661593605605</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.06166163975988481</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.09611430256490872</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.127673390178658</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.2090297194691594</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.2450600611652051</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.3457678584179134</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.3954915436963259</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.4441368507423509</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.5681273185846811</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.6167007922060335</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.7072648915167024</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.7816020577559278</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.7985423554551586</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.04137761724573641</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.06492630786531117</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.347181219848841</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.3876377273084176</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.472015704723236</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.5085023214787454</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.5996408004458869</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.6597872335807951</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.70191265135343</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7435181144991281</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.7659309557772922</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8002326119954608</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8345596377482658</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.872790209623343</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8908678431743652</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.007836597040745796</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.01969763205080866</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.04796567742957791</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.06244627774416867</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.1679381878370249</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.2750088810985736</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.404787255112401</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.4722291631621839</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.4931689460571317</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.5911180222895676</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.667604568027278</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.7251575505221248</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.7624873591658264</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.7803904229769627</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.7960870349088087</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.01980383558280785</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.06176560679326371</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.09841116670826255</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.3324852816599347</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.4133579315652824</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.5621447977868761</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.6025505795127939</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.6598277901795893</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.695193620180115</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.7235825108055167</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.7615058148598371</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.7806387379458956</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8024717832610795</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8166707638154656</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.839040291310185</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.01753722337279118</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.04840475005249478</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.09723254352825483</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.36845316144311</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.4321599094740276</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.5552510091836036</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.592615942512674</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.6608032818749004</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.6998668380629514</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7206095183040799</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7555295465643258</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.779399100499542</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8018987643096041</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8173332274557632</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8382870502874693</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.008149247996915188</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.02038637635081386</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.04030798391421497</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.07712077350222069</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.1033712297207263</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.2144341459995576</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.3080133592890911</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.4129143808596254</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.503471633765276</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.5188418738118062</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.6306418935227012</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.7277815083957963</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.7542253129958099</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.777767694526997</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.7948606455122003</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.01154569860863619</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.02005680848314739</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.04760606973304826</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.145268556092087</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.2176686626158466</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.3158692120900987</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.3788879374044499</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.4911978413626983</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.5350423856345181</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.6700157910879154</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.7054500226195228</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.7466154075976629</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.7696693015106494</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.7848539975877291</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.7992992862658402</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.01152313456493093</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.01991239859640215</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.04486120388122394</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.129367219507963</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.1919422206922079</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.2782630034682333</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.3312803443308547</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.4326303986671299</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.4641845967556236</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.6091709331912263</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.6515293836318006</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.6693354897140324</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.6925158353804789</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.7078322818994096</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.7340895419990188</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.01152168948984955</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.01991093147459011</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.04487432521330792</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.1287421374526238</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.190550449043809</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.2765967362649516</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.3284805653222311</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.428068693009273</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.4587118092132828</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.6017659980616903</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.6423419911025521</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.661932625463724</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.683731050313124</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.6959202369884018</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.7239230875084359</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.01152875063315162</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.01994316756941572</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.04519165179630469</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.1283375192472423</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.1891380719154154</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.2745861152790905</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.3284341747438898</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.4321981951388422</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.4667272134623552</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.606368998152762</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.6473398587196182</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.6693744127476636</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.6908687831951945</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7038732612611136</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.7234204418344667</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.02054951250612636</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.06198495345680577</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.09725879831196549</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.2785444640271529</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.4179340282554229</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.5057786907945625</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.600989989845832</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.6679626166691924</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7024941222736564</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.7279096002396117</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.7692896786244847</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.7892920497217275</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8106182018788173</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8252525092752536</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.848870212844166</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.02451161151884673</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.09309033201405537</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.1593498724788895</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.2520000001507794</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.3368146268315027</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.4651637963406741</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.5625095202106618</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.6107832328017928</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.6707984818876908</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.7189025793934112</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.7418392070501914</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.7749095030426005</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.7849186505555674</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.806605249120987</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8237738442266441</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.008142429455032074</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.0203278333571667</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.03904364454562903</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.07255859246028118</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.09593468645420489</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.1943365561156274</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.2765734059963531</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.3662826853506194</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.4552215937015605</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.5545527765393345</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.5691642387851588</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.6736252607475056</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.689820048121309</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.7210721326116291</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.7342878136826749</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.008138881981781143</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.02030998180629817</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.03868885261154609</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.07128465461445277</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.09372040560118811</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.1887039205189883</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.2689540771657162</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.3561684374270981</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.4453301254786658</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.535602642428441</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.5534872442316797</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.6578961297762784</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.6732652893878891</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.7026465377819764</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.7179214947100769</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.008134698502606619</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.02029008036855962</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.03837913643096091</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.07048984393610824</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.09251151693064164</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.1874397842780077</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.2680541659306787</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.3522770336667643</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.4396241709988072</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.4586775775626446</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.5483307266261324</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.6528417981149985</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.6701710093570457</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.7023307802662739</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.7183394340480568</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.008129854822600757</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.02028317956374293</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.0382282193647262</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.07019630189046988</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.09133205362736319</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.1841457011554151</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.2640051365502498</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.3413023645963188</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.4271411338631886</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.4717468540902103</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.5327219003772694</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.6278545308394519</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.6506021069098337</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.6871381589790835</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.7061548063468653</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.02049618379123497</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.06155000667198485</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.0964311393421754</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.2957576384512525</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.4042241232695819</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.5504453125755322</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.5900848865286905</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.6842508909295104</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.7142333728204222</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.7285815909858129</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.7666022211853074</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.7865679476892999</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8075789423114824</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.823145335387876</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.8467303167219143</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.01816923019189354</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.04794434664392333</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.09543007111450508</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.3394435911999218</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.4329701911952726</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.5468937765377913</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.5909165726633974</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.6496140023884673</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.6896756896535274</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.717117836206512</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.7585600298529962</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.7828720426978436</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8128434267375773</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8234682956652017</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8435564617653012</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.01742502591444228</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.04295361868756231</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.1231932549234488</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.2935912582754854</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.4091344131401702</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.5259094362877038</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.5656702486145948</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.6248712803400376</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.6482744087250398</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.6973765284668145</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7343334861291022</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.7599303312899317</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.7811983110573389</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.799336450346392</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8154730278679643</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.04108935684331005</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.06358032758058307</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.3201253916289433</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.3567984317121768</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.4353118094397266</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.4817901778630234</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.5834573040132247</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.6645088639738472</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7048801194918639</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.7504018787107722</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.7798332493346543</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8062939827744005</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8362643481834461</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.870205548531149</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8900924890189605</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.04102667169539653</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.06359150997037932</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.318784099158906</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.3543610566817569</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.4267902890840075</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.4692226270008075</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.5708339342251443</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.6426272872669806</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.6905244355357132</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.7374733085441871</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.7798972321640226</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8115929748250653</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8440106584662517</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8636842162647203</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8802548337062048</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.02599067419987988</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.1250768615259352</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.240000806404908</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.3218031678737291</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.5402034937334093</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.6274561829853995</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.6821213281629086</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.741616366734773</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7708881097611017</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.816847390297968</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8470927786087649</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8822534255278314</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8952594039181703</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9111800083870538</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.928464740122995</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.08845781937087349</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.1310283386771761</v>
+        <v>0.004024106045102505</v>
       </c>
       <c r="D24">
-        <v>0.1921474885679809</v>
+        <v>0.02386009143528012</v>
       </c>
       <c r="E24">
-        <v>0.2595394112614237</v>
+        <v>0.04077924193293503</v>
       </c>
       <c r="F24">
-        <v>0.3375022758985636</v>
+        <v>0.06930244464398294</v>
       </c>
       <c r="G24">
-        <v>0.4883839756532843</v>
+        <v>0.1040941899635768</v>
       </c>
       <c r="H24">
-        <v>0.5242402657756895</v>
+        <v>0.1668893751776583</v>
       </c>
       <c r="I24">
-        <v>0.5831141685899213</v>
+        <v>0.2163266336632435</v>
       </c>
       <c r="J24">
-        <v>0.6219117265425675</v>
+        <v>0.3903010081781513</v>
       </c>
       <c r="K24">
-        <v>0.675573278844645</v>
+        <v>0.5989974288689471</v>
       </c>
       <c r="L24">
-        <v>0.7018633558702272</v>
+        <v>0.658126669164246</v>
       </c>
       <c r="M24">
-        <v>0.7410229903767448</v>
+        <v>0.7087055116142482</v>
       </c>
       <c r="N24">
-        <v>0.7856997623081157</v>
+        <v>0.7738171140556058</v>
       </c>
       <c r="O24">
-        <v>0.8200338078515773</v>
+        <v>0.8289912654399119</v>
       </c>
       <c r="P24">
-        <v>0.8483158542573198</v>
+        <v>0.854054123225453</v>
+      </c>
+      <c r="Q24">
+        <v>0.873831341956929</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.1965900073563476</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.2757338169188629</v>
+        <v>0.004309423043286409</v>
       </c>
       <c r="D25">
-        <v>0.355430022662553</v>
+        <v>0.03237831125058521</v>
       </c>
       <c r="E25">
-        <v>0.4145948366213512</v>
+        <v>0.05585819661913649</v>
       </c>
       <c r="F25">
-        <v>0.4719103779209991</v>
+        <v>0.0911658690639281</v>
       </c>
       <c r="G25">
-        <v>0.5172889685336535</v>
+        <v>0.100538020179238</v>
       </c>
       <c r="H25">
-        <v>0.5752928707076947</v>
+        <v>0.1492382330199343</v>
       </c>
       <c r="I25">
-        <v>0.642585775462752</v>
+        <v>0.1952794039534389</v>
       </c>
       <c r="J25">
-        <v>0.672286866119681</v>
+        <v>0.4082462350904972</v>
       </c>
       <c r="K25">
-        <v>0.7228039122343426</v>
+        <v>0.4804746026009773</v>
       </c>
       <c r="L25">
-        <v>0.7572896386978109</v>
+        <v>0.6520414535918574</v>
       </c>
       <c r="M25">
-        <v>0.8014840204090976</v>
+        <v>0.6808988619369847</v>
       </c>
       <c r="N25">
-        <v>0.8313808794236043</v>
+        <v>0.73885717335773</v>
       </c>
       <c r="O25">
-        <v>0.8564750284131686</v>
+        <v>0.7841730233447172</v>
       </c>
       <c r="P25">
-        <v>0.8748107440554719</v>
+        <v>0.8353257288558364</v>
+      </c>
+      <c r="Q25">
+        <v>0.8545708535337754</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.06102689923619486</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1721715647470122</v>
+        <v>0.004511575802238155</v>
       </c>
       <c r="D26">
-        <v>0.1822666275521259</v>
+        <v>0.04298657733523348</v>
       </c>
       <c r="E26">
-        <v>0.2061505071219544</v>
+        <v>0.05384606310758211</v>
       </c>
       <c r="F26">
-        <v>0.3292173700322648</v>
+        <v>0.09382877613019602</v>
       </c>
       <c r="G26">
-        <v>0.3665742452188462</v>
+        <v>0.1275644276607656</v>
       </c>
       <c r="H26">
-        <v>0.398693000734348</v>
+        <v>0.1738278310711359</v>
       </c>
       <c r="I26">
-        <v>0.4700625630355364</v>
+        <v>0.3826207309866966</v>
       </c>
       <c r="J26">
-        <v>0.5085785647505592</v>
+        <v>0.5394091989830625</v>
       </c>
       <c r="K26">
-        <v>0.5770256858091691</v>
+        <v>0.596174050900568</v>
       </c>
       <c r="L26">
-        <v>0.599879495730465</v>
+        <v>0.6859949262647009</v>
       </c>
       <c r="M26">
-        <v>0.6316923513236788</v>
+        <v>0.7334970128587366</v>
       </c>
       <c r="N26">
-        <v>0.6574949199441449</v>
+        <v>0.7997864529058215</v>
       </c>
       <c r="O26">
-        <v>0.7092394194898242</v>
+        <v>0.8323180962943092</v>
       </c>
       <c r="P26">
-        <v>0.7408739604665946</v>
+        <v>0.8514951305256984</v>
+      </c>
+      <c r="Q26">
+        <v>0.8795196506347119</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.0677585651005731</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.1180636698500195</v>
+        <v>0.004468236546673943</v>
       </c>
       <c r="D27">
-        <v>0.2379987968736582</v>
+        <v>0.03994961915976381</v>
       </c>
       <c r="E27">
-        <v>0.2538036292843906</v>
+        <v>0.04933651284077079</v>
       </c>
       <c r="F27">
-        <v>0.3648967161355159</v>
+        <v>0.08122702694318107</v>
       </c>
       <c r="G27">
-        <v>0.415303802335098</v>
+        <v>0.1063328784705342</v>
       </c>
       <c r="H27">
-        <v>0.4727393273829212</v>
+        <v>0.1359296249785293</v>
       </c>
       <c r="I27">
-        <v>0.5560760720124971</v>
+        <v>0.2654163157765536</v>
       </c>
       <c r="J27">
-        <v>0.6284661076960245</v>
+        <v>0.3840890470076562</v>
       </c>
       <c r="K27">
-        <v>0.6626420457452546</v>
+        <v>0.4502150183085093</v>
       </c>
       <c r="L27">
-        <v>0.6745374336241068</v>
+        <v>0.5612329342567495</v>
       </c>
       <c r="M27">
-        <v>0.7080440278655629</v>
+        <v>0.5887808312085722</v>
       </c>
       <c r="N27">
-        <v>0.7419926787049214</v>
+        <v>0.6473118150927852</v>
       </c>
       <c r="O27">
-        <v>0.7708188149551825</v>
+        <v>0.6691240787142643</v>
       </c>
       <c r="P27">
-        <v>0.7854194197211364</v>
+        <v>0.6965298643550879</v>
+      </c>
+      <c r="Q27">
+        <v>0.7141343423912969</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.004024106045102505</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.02386009143528012</v>
+        <v>0.00427159123711629</v>
       </c>
       <c r="D28">
-        <v>0.04077924193293503</v>
+        <v>0.03006462353989559</v>
       </c>
       <c r="E28">
-        <v>0.06930244464398294</v>
+        <v>0.0515814563677236</v>
       </c>
       <c r="F28">
-        <v>0.1040941899635768</v>
+        <v>0.07999651715970613</v>
       </c>
       <c r="G28">
-        <v>0.1668893751776583</v>
+        <v>0.08690281317591264</v>
       </c>
       <c r="H28">
-        <v>0.2163266336632435</v>
+        <v>0.1191872070461673</v>
       </c>
       <c r="I28">
-        <v>0.3903010081781513</v>
+        <v>0.1436130523595676</v>
       </c>
       <c r="J28">
-        <v>0.5989974288689471</v>
+        <v>0.2828716926810672</v>
       </c>
       <c r="K28">
-        <v>0.658126669164246</v>
+        <v>0.3426432595422696</v>
       </c>
       <c r="L28">
-        <v>0.7087055116142482</v>
+        <v>0.5460620301653192</v>
       </c>
       <c r="M28">
-        <v>0.7738171140556058</v>
+        <v>0.5653670413906557</v>
       </c>
       <c r="N28">
-        <v>0.8289912654399119</v>
+        <v>0.5850188627355899</v>
       </c>
       <c r="O28">
-        <v>0.854054123225453</v>
+        <v>0.6347106404948712</v>
       </c>
       <c r="P28">
-        <v>0.873831341956929</v>
+        <v>0.6658325874848765</v>
+      </c>
+      <c r="Q28">
+        <v>0.6934459024298216</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.004309423043286409</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.03237831125058521</v>
+        <v>0.004273917638383917</v>
       </c>
       <c r="D29">
-        <v>0.05585819661913649</v>
+        <v>0.03010160907394832</v>
       </c>
       <c r="E29">
-        <v>0.0911658690639281</v>
+        <v>0.05159401144055265</v>
       </c>
       <c r="F29">
-        <v>0.100538020179238</v>
+        <v>0.08019840410814372</v>
       </c>
       <c r="G29">
-        <v>0.1492382330199343</v>
+        <v>0.08699328102900283</v>
       </c>
       <c r="H29">
-        <v>0.1952794039534389</v>
+        <v>0.1191538987768315</v>
       </c>
       <c r="I29">
-        <v>0.4082462350904972</v>
+        <v>0.1433390331107028</v>
       </c>
       <c r="J29">
-        <v>0.4804746026009773</v>
+        <v>0.2795402238791156</v>
       </c>
       <c r="K29">
-        <v>0.6520414535918574</v>
+        <v>0.3401080450516358</v>
       </c>
       <c r="L29">
-        <v>0.6808988619369847</v>
+        <v>0.5437818022109088</v>
       </c>
       <c r="M29">
-        <v>0.73885717335773</v>
+        <v>0.5608692027986228</v>
       </c>
       <c r="N29">
-        <v>0.7841730233447172</v>
+        <v>0.5804525739369102</v>
       </c>
       <c r="O29">
-        <v>0.8353257288558364</v>
+        <v>0.6305071425737885</v>
       </c>
       <c r="P29">
-        <v>0.8545708535337754</v>
+        <v>0.6630349255363768</v>
+      </c>
+      <c r="Q29">
+        <v>0.6904020418848849</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.004511575802238155</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.04298657733523348</v>
+        <v>0.004268206225499505</v>
       </c>
       <c r="D30">
-        <v>0.05384606310758211</v>
+        <v>0.02979636164927768</v>
       </c>
       <c r="E30">
-        <v>0.09382877613019602</v>
+        <v>0.05109753088457525</v>
       </c>
       <c r="F30">
-        <v>0.1275644276607656</v>
+        <v>0.07890300042039222</v>
       </c>
       <c r="G30">
-        <v>0.1738278310711359</v>
+        <v>0.08583229403234871</v>
       </c>
       <c r="H30">
-        <v>0.3826207309866966</v>
+        <v>0.1170728819946687</v>
       </c>
       <c r="I30">
-        <v>0.5394091989830625</v>
+        <v>0.1401136556292656</v>
       </c>
       <c r="J30">
-        <v>0.596174050900568</v>
+        <v>0.2733711188877879</v>
       </c>
       <c r="K30">
-        <v>0.6859949262647009</v>
+        <v>0.3355075430412497</v>
       </c>
       <c r="L30">
-        <v>0.7334970128587366</v>
+        <v>0.5374117908274798</v>
       </c>
       <c r="M30">
-        <v>0.7997864529058215</v>
+        <v>0.5538972245664731</v>
       </c>
       <c r="N30">
-        <v>0.8323180962943092</v>
+        <v>0.5719122784040479</v>
       </c>
       <c r="O30">
-        <v>0.8514951305256984</v>
+        <v>0.6238126752427025</v>
       </c>
       <c r="P30">
-        <v>0.8795196506347119</v>
+        <v>0.6587469206548447</v>
+      </c>
+      <c r="Q30">
+        <v>0.6848813850821138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.004468236546673943</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.03994961915976381</v>
+        <v>0.004258807347848559</v>
       </c>
       <c r="D31">
-        <v>0.04933651284077079</v>
+        <v>0.02934379951341792</v>
       </c>
       <c r="E31">
-        <v>0.08122702694318107</v>
+        <v>0.0503934328734551</v>
       </c>
       <c r="F31">
-        <v>0.1063328784705342</v>
+        <v>0.07691518712105905</v>
       </c>
       <c r="G31">
-        <v>0.1359296249785293</v>
+        <v>0.08421427205764365</v>
       </c>
       <c r="H31">
-        <v>0.2654163157765536</v>
+        <v>0.114026985842452</v>
       </c>
       <c r="I31">
-        <v>0.3840890470076562</v>
+        <v>0.1353526667220273</v>
       </c>
       <c r="J31">
-        <v>0.4502150183085093</v>
+        <v>0.2611393889681974</v>
       </c>
       <c r="K31">
-        <v>0.5612329342567495</v>
+        <v>0.3265263738278679</v>
       </c>
       <c r="L31">
-        <v>0.5887808312085722</v>
+        <v>0.5290370001838085</v>
       </c>
       <c r="M31">
-        <v>0.6473118150927852</v>
+        <v>0.5474317120404038</v>
       </c>
       <c r="N31">
-        <v>0.6691240787142643</v>
+        <v>0.5607312830481477</v>
       </c>
       <c r="O31">
-        <v>0.6965298643550879</v>
+        <v>0.6143459554952154</v>
       </c>
       <c r="P31">
-        <v>0.7141343423912969</v>
+        <v>0.6562354190144466</v>
+      </c>
+      <c r="Q31">
+        <v>0.6804861684906053</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.00427159123711629</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.03006462353989559</v>
+        <v>0.004281808004088505</v>
       </c>
       <c r="D32">
-        <v>0.0515814563677236</v>
+        <v>0.0306274095508392</v>
       </c>
       <c r="E32">
-        <v>0.07999651715970613</v>
+        <v>0.05259677804785934</v>
       </c>
       <c r="F32">
-        <v>0.08690281317591264</v>
+        <v>0.08248288943629511</v>
       </c>
       <c r="G32">
-        <v>0.1191872070461673</v>
+        <v>0.08958234779747898</v>
       </c>
       <c r="H32">
-        <v>0.1436130523595676</v>
+        <v>0.1242276730807036</v>
       </c>
       <c r="I32">
-        <v>0.2828716926810672</v>
+        <v>0.1515284979596904</v>
       </c>
       <c r="J32">
-        <v>0.3426432595422696</v>
+        <v>0.2977650097215064</v>
       </c>
       <c r="K32">
-        <v>0.5460620301653192</v>
+        <v>0.3565492897941709</v>
       </c>
       <c r="L32">
-        <v>0.5653670413906557</v>
+        <v>0.5604155880405496</v>
       </c>
       <c r="M32">
-        <v>0.5850188627355899</v>
+        <v>0.5791346332331774</v>
       </c>
       <c r="N32">
-        <v>0.6347106404948712</v>
+        <v>0.6031117926669733</v>
       </c>
       <c r="O32">
-        <v>0.6658325874848765</v>
+        <v>0.6519502413852558</v>
       </c>
       <c r="P32">
-        <v>0.6934459024298216</v>
+        <v>0.688737395498674</v>
+      </c>
+      <c r="Q32">
+        <v>0.7233641070110091</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.004273917638383917</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.03010160907394832</v>
+        <v>0.004279040750468366</v>
       </c>
       <c r="D33">
-        <v>0.05159401144055265</v>
+        <v>0.0304478541674057</v>
       </c>
       <c r="E33">
-        <v>0.08019840410814372</v>
+        <v>0.05224369130174744</v>
       </c>
       <c r="F33">
-        <v>0.08699328102900283</v>
+        <v>0.08160178238463744</v>
       </c>
       <c r="G33">
-        <v>0.1191538987768315</v>
+        <v>0.08858940037286478</v>
       </c>
       <c r="H33">
-        <v>0.1433390331107028</v>
+        <v>0.1222752070789668</v>
       </c>
       <c r="I33">
-        <v>0.2795402238791156</v>
+        <v>0.14837028136149</v>
       </c>
       <c r="J33">
-        <v>0.3401080450516358</v>
+        <v>0.2905990387131731</v>
       </c>
       <c r="K33">
-        <v>0.5437818022109088</v>
+        <v>0.3490345774403918</v>
       </c>
       <c r="L33">
-        <v>0.5608692027986228</v>
+        <v>0.5561912363114165</v>
       </c>
       <c r="M33">
-        <v>0.5804525739369102</v>
+        <v>0.5755772847046028</v>
       </c>
       <c r="N33">
-        <v>0.6305071425737885</v>
+        <v>0.5987897507791696</v>
       </c>
       <c r="O33">
-        <v>0.6630349255363768</v>
+        <v>0.6451283697934758</v>
       </c>
       <c r="P33">
-        <v>0.6904020418848849</v>
+        <v>0.6819351328332548</v>
+      </c>
+      <c r="Q33">
+        <v>0.7166668820957353</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.004268206225499505</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.02979636164927768</v>
+        <v>0.004277046288847175</v>
       </c>
       <c r="D34">
-        <v>0.05109753088457525</v>
+        <v>0.03030904233090737</v>
       </c>
       <c r="E34">
-        <v>0.07890300042039222</v>
+        <v>0.05194539605419002</v>
       </c>
       <c r="F34">
-        <v>0.08583229403234871</v>
+        <v>0.08093158931686573</v>
       </c>
       <c r="G34">
-        <v>0.1170728819946687</v>
+        <v>0.08783328489683473</v>
       </c>
       <c r="H34">
-        <v>0.1401136556292656</v>
+        <v>0.1207537701050124</v>
       </c>
       <c r="I34">
-        <v>0.2733711188877879</v>
+        <v>0.1457783501640263</v>
       </c>
       <c r="J34">
-        <v>0.3355075430412497</v>
+        <v>0.2834114636922581</v>
       </c>
       <c r="K34">
-        <v>0.5374117908274798</v>
+        <v>0.341587181666728</v>
       </c>
       <c r="L34">
-        <v>0.5538972245664731</v>
+        <v>0.5536917589081003</v>
       </c>
       <c r="M34">
-        <v>0.5719122784040479</v>
+        <v>0.5726595186460037</v>
       </c>
       <c r="N34">
-        <v>0.6238126752427025</v>
+        <v>0.5945898773107957</v>
       </c>
       <c r="O34">
-        <v>0.6587469206548447</v>
+        <v>0.6391793787743935</v>
       </c>
       <c r="P34">
-        <v>0.6848813850821138</v>
+        <v>0.6764744230681816</v>
+      </c>
+      <c r="Q34">
+        <v>0.7070456869797423</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.004258807347848559</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.02934379951341792</v>
+        <v>0.004276411745970154</v>
       </c>
       <c r="D35">
-        <v>0.0503934328734551</v>
+        <v>0.03022108980082738</v>
       </c>
       <c r="E35">
-        <v>0.07691518712105905</v>
+        <v>0.05175125402239389</v>
       </c>
       <c r="F35">
-        <v>0.08421427205764365</v>
+        <v>0.08055150956896973</v>
       </c>
       <c r="G35">
-        <v>0.114026985842452</v>
+        <v>0.08744542453443982</v>
       </c>
       <c r="H35">
-        <v>0.1353526667220273</v>
+        <v>0.1199948009518418</v>
       </c>
       <c r="I35">
-        <v>0.2611393889681974</v>
+        <v>0.1443712916351968</v>
       </c>
       <c r="J35">
-        <v>0.3265263738278679</v>
+        <v>0.2791228996948314</v>
       </c>
       <c r="K35">
-        <v>0.5290370001838085</v>
+        <v>0.3369810026194464</v>
       </c>
       <c r="L35">
-        <v>0.5474317120404038</v>
+        <v>0.5489795080566745</v>
       </c>
       <c r="M35">
-        <v>0.5607312830481477</v>
+        <v>0.5670508026014007</v>
       </c>
       <c r="N35">
-        <v>0.6143459554952154</v>
+        <v>0.5868757909362229</v>
       </c>
       <c r="O35">
-        <v>0.6562354190144466</v>
+        <v>0.6287809584353442</v>
       </c>
       <c r="P35">
-        <v>0.6804861684906053</v>
+        <v>0.6650759205489915</v>
+      </c>
+      <c r="Q35">
+        <v>0.69230549287569</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.004281808004088505</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.0306274095508392</v>
+        <v>0.004270031210824476</v>
       </c>
       <c r="D36">
-        <v>0.05259677804785934</v>
+        <v>0.02978600407566256</v>
       </c>
       <c r="E36">
-        <v>0.08248288943629511</v>
+        <v>0.05089102508455934</v>
       </c>
       <c r="F36">
-        <v>0.08958234779747898</v>
+        <v>0.07894240222782611</v>
       </c>
       <c r="G36">
-        <v>0.1242276730807036</v>
+        <v>0.08578786515929493</v>
       </c>
       <c r="H36">
-        <v>0.1515284979596904</v>
+        <v>0.1166548522380634</v>
       </c>
       <c r="I36">
-        <v>0.2977650097215064</v>
+        <v>0.1387440168570634</v>
       </c>
       <c r="J36">
-        <v>0.3565492897941709</v>
+        <v>0.2619429160337043</v>
       </c>
       <c r="K36">
-        <v>0.5604155880405496</v>
+        <v>0.3238516686392932</v>
       </c>
       <c r="L36">
-        <v>0.5791346332331774</v>
+        <v>0.5258190191226004</v>
       </c>
       <c r="M36">
-        <v>0.6031117926669733</v>
+        <v>0.5511301573220877</v>
       </c>
       <c r="N36">
-        <v>0.6519502413852558</v>
+        <v>0.5662900793522945</v>
       </c>
       <c r="O36">
-        <v>0.688737395498674</v>
+        <v>0.6062322621761156</v>
       </c>
       <c r="P36">
-        <v>0.7233641070110091</v>
+        <v>0.6508113784029386</v>
+      </c>
+      <c r="Q36">
+        <v>0.6789380197197723</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.004279040750468366</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.0304478541674057</v>
+        <v>0.00806850257902969</v>
       </c>
       <c r="D37">
-        <v>0.05224369130174744</v>
+        <v>0.1299520233770577</v>
       </c>
       <c r="E37">
-        <v>0.08160178238463744</v>
+        <v>0.157684127344583</v>
       </c>
       <c r="F37">
-        <v>0.08858940037286478</v>
+        <v>0.2332926386011963</v>
       </c>
       <c r="G37">
-        <v>0.1222752070789668</v>
+        <v>0.4019382314400769</v>
       </c>
       <c r="H37">
-        <v>0.14837028136149</v>
+        <v>0.4859101272766783</v>
       </c>
       <c r="I37">
-        <v>0.2905990387131731</v>
+        <v>0.6060942901924251</v>
       </c>
       <c r="J37">
-        <v>0.3490345774403918</v>
+        <v>0.6329827956448845</v>
       </c>
       <c r="K37">
-        <v>0.5561912363114165</v>
+        <v>0.6777493466683268</v>
       </c>
       <c r="L37">
-        <v>0.5755772847046028</v>
+        <v>0.7404422358242251</v>
       </c>
       <c r="M37">
-        <v>0.5987897507791696</v>
+        <v>0.7785396303703038</v>
       </c>
       <c r="N37">
-        <v>0.6451283697934758</v>
+        <v>0.8154559217278898</v>
       </c>
       <c r="O37">
-        <v>0.6819351328332548</v>
+        <v>0.8445691323386892</v>
       </c>
       <c r="P37">
-        <v>0.7166668820957353</v>
+        <v>0.8629194607867747</v>
+      </c>
+      <c r="Q37">
+        <v>0.8728603160935637</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.004277046288847175</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.03030904233090737</v>
+        <v>0.005412661314427969</v>
       </c>
       <c r="D38">
-        <v>0.05194539605419002</v>
+        <v>0.07481637422829035</v>
       </c>
       <c r="E38">
-        <v>0.08093158931686573</v>
+        <v>0.09896349267256033</v>
       </c>
       <c r="F38">
-        <v>0.08783328489683473</v>
+        <v>0.232243530513833</v>
       </c>
       <c r="G38">
-        <v>0.1207537701050124</v>
+        <v>0.4116130667095645</v>
       </c>
       <c r="H38">
-        <v>0.1457783501640263</v>
+        <v>0.4826707302957779</v>
       </c>
       <c r="I38">
-        <v>0.2834114636922581</v>
+        <v>0.5271093084280798</v>
       </c>
       <c r="J38">
-        <v>0.341587181666728</v>
+        <v>0.5718440245545888</v>
       </c>
       <c r="K38">
-        <v>0.5536917589081003</v>
+        <v>0.6217196373230044</v>
       </c>
       <c r="L38">
-        <v>0.5726595186460037</v>
+        <v>0.6513176745363918</v>
       </c>
       <c r="M38">
-        <v>0.5945898773107957</v>
+        <v>0.6985399350656422</v>
       </c>
       <c r="N38">
-        <v>0.6391793787743935</v>
+        <v>0.7348916465808258</v>
       </c>
       <c r="O38">
-        <v>0.6764744230681816</v>
+        <v>0.7752336431307504</v>
       </c>
       <c r="P38">
-        <v>0.7070456869797423</v>
+        <v>0.8117324443501638</v>
+      </c>
+      <c r="Q38">
+        <v>0.8332971542273826</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.004276411745970154</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.03022108980082738</v>
+        <v>0.005529065439923819</v>
       </c>
       <c r="D39">
-        <v>0.05175125402239389</v>
+        <v>0.0738217420430014</v>
       </c>
       <c r="E39">
-        <v>0.08055150956896973</v>
+        <v>0.09284542237286431</v>
       </c>
       <c r="F39">
-        <v>0.08744542453443982</v>
+        <v>0.197261889210572</v>
       </c>
       <c r="G39">
-        <v>0.1199948009518418</v>
+        <v>0.3198389143792864</v>
       </c>
       <c r="H39">
-        <v>0.1443712916351968</v>
+        <v>0.3921755545519374</v>
       </c>
       <c r="I39">
-        <v>0.2791228996948314</v>
+        <v>0.4827829506650637</v>
       </c>
       <c r="J39">
-        <v>0.3369810026194464</v>
+        <v>0.5257897676835794</v>
       </c>
       <c r="K39">
-        <v>0.5489795080566745</v>
+        <v>0.5957670686250967</v>
       </c>
       <c r="L39">
-        <v>0.5670508026014007</v>
+        <v>0.617507158847668</v>
       </c>
       <c r="M39">
-        <v>0.5868757909362229</v>
+        <v>0.6515406186533415</v>
       </c>
       <c r="N39">
-        <v>0.6287809584353442</v>
+        <v>0.6926819377512371</v>
       </c>
       <c r="O39">
-        <v>0.6650759205489915</v>
+        <v>0.7380339595328205</v>
       </c>
       <c r="P39">
-        <v>0.69230549287569</v>
+        <v>0.7706795906777266</v>
+      </c>
+      <c r="Q39">
+        <v>0.8058580786669516</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.004270031210824476</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.02978600407566256</v>
+        <v>0.01395523663929743</v>
       </c>
       <c r="D40">
-        <v>0.05089102508455934</v>
+        <v>0.04782731656612071</v>
       </c>
       <c r="E40">
-        <v>0.07894240222782611</v>
+        <v>0.2218584575686143</v>
       </c>
       <c r="F40">
-        <v>0.08578786515929493</v>
+        <v>0.2463732798457554</v>
       </c>
       <c r="G40">
-        <v>0.1166548522380634</v>
+        <v>0.4380918496702108</v>
       </c>
       <c r="H40">
-        <v>0.1387440168570634</v>
+        <v>0.5212860475259926</v>
       </c>
       <c r="I40">
-        <v>0.2619429160337043</v>
+        <v>0.5780405635720323</v>
       </c>
       <c r="J40">
-        <v>0.3238516686392932</v>
+        <v>0.6602622029370734</v>
       </c>
       <c r="K40">
-        <v>0.5258190191226004</v>
+        <v>0.7076498547021299</v>
       </c>
       <c r="L40">
-        <v>0.5511301573220877</v>
+        <v>0.7582031083283017</v>
       </c>
       <c r="M40">
-        <v>0.5662900793522945</v>
+        <v>0.7804776868764784</v>
       </c>
       <c r="N40">
-        <v>0.6062322621761156</v>
+        <v>0.8056414282989681</v>
       </c>
       <c r="O40">
-        <v>0.6508113784029386</v>
+        <v>0.8278370941426234</v>
       </c>
       <c r="P40">
-        <v>0.6789380197197723</v>
+        <v>0.8480156663934481</v>
+      </c>
+      <c r="Q40">
+        <v>0.8695398912896223</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.00806850257902969</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.1299520233770577</v>
+        <v>0.05147895604695329</v>
       </c>
       <c r="D41">
-        <v>0.157684127344583</v>
+        <v>0.2123324763072013</v>
       </c>
       <c r="E41">
-        <v>0.2332926386011963</v>
+        <v>0.3529476338755499</v>
       </c>
       <c r="F41">
-        <v>0.4019382314400769</v>
+        <v>0.4248654367957254</v>
       </c>
       <c r="G41">
-        <v>0.4859101272766783</v>
+        <v>0.5168561306056348</v>
       </c>
       <c r="H41">
-        <v>0.6060942901924251</v>
+        <v>0.5617223327239577</v>
       </c>
       <c r="I41">
-        <v>0.6329827956448845</v>
+        <v>0.6370135316239076</v>
       </c>
       <c r="J41">
-        <v>0.6777493466683268</v>
+        <v>0.6757191304422365</v>
       </c>
       <c r="K41">
-        <v>0.7404422358242251</v>
+        <v>0.7108674019558909</v>
       </c>
       <c r="L41">
-        <v>0.7785396303703038</v>
+        <v>0.7524667813365058</v>
       </c>
       <c r="M41">
-        <v>0.8154559217278898</v>
+        <v>0.779099644199388</v>
       </c>
       <c r="N41">
-        <v>0.8445691323386892</v>
+        <v>0.816357834897663</v>
       </c>
       <c r="O41">
-        <v>0.8629194607867747</v>
+        <v>0.8414946047440314</v>
       </c>
       <c r="P41">
-        <v>0.8728603160935637</v>
+        <v>0.8640375127989137</v>
+      </c>
+      <c r="Q41">
+        <v>0.8834465646411541</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.005412661314427969</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.07481637422829035</v>
+        <v>0.04607334055647216</v>
       </c>
       <c r="D42">
-        <v>0.09896349267256033</v>
+        <v>0.09430810554446689</v>
       </c>
       <c r="E42">
-        <v>0.232243530513833</v>
+        <v>0.3186900947615909</v>
       </c>
       <c r="F42">
-        <v>0.4116130667095645</v>
+        <v>0.4544330926787558</v>
       </c>
       <c r="G42">
-        <v>0.4826707302957779</v>
+        <v>0.5691128220095524</v>
       </c>
       <c r="H42">
-        <v>0.5271093084280798</v>
+        <v>0.6384772140733237</v>
       </c>
       <c r="I42">
-        <v>0.5718440245545888</v>
+        <v>0.704627052934955</v>
       </c>
       <c r="J42">
-        <v>0.6217196373230044</v>
+        <v>0.7472863569662325</v>
       </c>
       <c r="K42">
-        <v>0.6513176745363918</v>
+        <v>0.7702350386163898</v>
       </c>
       <c r="L42">
-        <v>0.6985399350656422</v>
+        <v>0.8051239897275936</v>
       </c>
       <c r="M42">
-        <v>0.7348916465808258</v>
+        <v>0.8323197029175523</v>
       </c>
       <c r="N42">
-        <v>0.7752336431307504</v>
+        <v>0.8648101344012777</v>
       </c>
       <c r="O42">
-        <v>0.8117324443501638</v>
+        <v>0.8912150546165747</v>
       </c>
       <c r="P42">
-        <v>0.8332971542273826</v>
+        <v>0.8995085057956776</v>
+      </c>
+      <c r="Q42">
+        <v>0.91740578922838</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.005529065439923819</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.0738217420430014</v>
+        <v>0.02850711830779029</v>
       </c>
       <c r="D43">
-        <v>0.09284542237286431</v>
+        <v>0.1328664925923085</v>
       </c>
       <c r="E43">
-        <v>0.197261889210572</v>
+        <v>0.3107462117928</v>
       </c>
       <c r="F43">
-        <v>0.3198389143792864</v>
+        <v>0.4424440709110021</v>
       </c>
       <c r="G43">
-        <v>0.3921755545519374</v>
+        <v>0.5434672393310999</v>
       </c>
       <c r="H43">
-        <v>0.4827829506650637</v>
+        <v>0.5829974480750847</v>
       </c>
       <c r="I43">
-        <v>0.5257897676835794</v>
+        <v>0.6436607103637738</v>
       </c>
       <c r="J43">
-        <v>0.5957670686250967</v>
+        <v>0.6960758872351608</v>
       </c>
       <c r="K43">
-        <v>0.617507158847668</v>
+        <v>0.7528593865477613</v>
       </c>
       <c r="L43">
-        <v>0.6515406186533415</v>
+        <v>0.7950415290543877</v>
       </c>
       <c r="M43">
-        <v>0.6926819377512371</v>
+        <v>0.8251969668390378</v>
       </c>
       <c r="N43">
-        <v>0.7380339595328205</v>
+        <v>0.8527149875534512</v>
       </c>
       <c r="O43">
-        <v>0.7706795906777266</v>
+        <v>0.869104366587707</v>
       </c>
       <c r="P43">
-        <v>0.8058580786669516</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.01395523663929743</v>
-      </c>
-      <c r="C44">
-        <v>0.04782731656612071</v>
-      </c>
-      <c r="D44">
-        <v>0.2218584575686143</v>
-      </c>
-      <c r="E44">
-        <v>0.2463732798457554</v>
-      </c>
-      <c r="F44">
-        <v>0.4380918496702108</v>
-      </c>
-      <c r="G44">
-        <v>0.5212860475259926</v>
-      </c>
-      <c r="H44">
-        <v>0.5780405635720323</v>
-      </c>
-      <c r="I44">
-        <v>0.6602622029370734</v>
-      </c>
-      <c r="J44">
-        <v>0.7076498547021299</v>
-      </c>
-      <c r="K44">
-        <v>0.7582031083283017</v>
-      </c>
-      <c r="L44">
-        <v>0.7804776868764784</v>
-      </c>
-      <c r="M44">
-        <v>0.8056414282989681</v>
-      </c>
-      <c r="N44">
-        <v>0.8278370941426234</v>
-      </c>
-      <c r="O44">
-        <v>0.8480156663934481</v>
-      </c>
-      <c r="P44">
-        <v>0.8695398912896223</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.05147895604695329</v>
-      </c>
-      <c r="C45">
-        <v>0.2123324763072013</v>
-      </c>
-      <c r="D45">
-        <v>0.3529476338755499</v>
-      </c>
-      <c r="E45">
-        <v>0.4248654367957254</v>
-      </c>
-      <c r="F45">
-        <v>0.5168561306056348</v>
-      </c>
-      <c r="G45">
-        <v>0.5617223327239577</v>
-      </c>
-      <c r="H45">
-        <v>0.6370135316239076</v>
-      </c>
-      <c r="I45">
-        <v>0.6757191304422365</v>
-      </c>
-      <c r="J45">
-        <v>0.7108674019558909</v>
-      </c>
-      <c r="K45">
-        <v>0.7524667813365058</v>
-      </c>
-      <c r="L45">
-        <v>0.779099644199388</v>
-      </c>
-      <c r="M45">
-        <v>0.816357834897663</v>
-      </c>
-      <c r="N45">
-        <v>0.8414946047440314</v>
-      </c>
-      <c r="O45">
-        <v>0.8640375127989137</v>
-      </c>
-      <c r="P45">
-        <v>0.8834465646411541</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.04607334055647216</v>
-      </c>
-      <c r="C46">
-        <v>0.09430810554446689</v>
-      </c>
-      <c r="D46">
-        <v>0.3186900947615909</v>
-      </c>
-      <c r="E46">
-        <v>0.4544330926787558</v>
-      </c>
-      <c r="F46">
-        <v>0.5691128220095524</v>
-      </c>
-      <c r="G46">
-        <v>0.6384772140733237</v>
-      </c>
-      <c r="H46">
-        <v>0.704627052934955</v>
-      </c>
-      <c r="I46">
-        <v>0.7472863569662325</v>
-      </c>
-      <c r="J46">
-        <v>0.7702350386163898</v>
-      </c>
-      <c r="K46">
-        <v>0.8051239897275936</v>
-      </c>
-      <c r="L46">
-        <v>0.8323197029175523</v>
-      </c>
-      <c r="M46">
-        <v>0.8648101344012777</v>
-      </c>
-      <c r="N46">
-        <v>0.8912150546165747</v>
-      </c>
-      <c r="O46">
-        <v>0.8995085057956776</v>
-      </c>
-      <c r="P46">
-        <v>0.91740578922838</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.02850711830779029</v>
-      </c>
-      <c r="C47">
-        <v>0.1328664925923085</v>
-      </c>
-      <c r="D47">
-        <v>0.3107462117928</v>
-      </c>
-      <c r="E47">
-        <v>0.4424440709110021</v>
-      </c>
-      <c r="F47">
-        <v>0.5434672393310999</v>
-      </c>
-      <c r="G47">
-        <v>0.5829974480750847</v>
-      </c>
-      <c r="H47">
-        <v>0.6436607103637738</v>
-      </c>
-      <c r="I47">
-        <v>0.6960758872351608</v>
-      </c>
-      <c r="J47">
-        <v>0.7528593865477613</v>
-      </c>
-      <c r="K47">
-        <v>0.7950415290543877</v>
-      </c>
-      <c r="L47">
-        <v>0.8251969668390378</v>
-      </c>
-      <c r="M47">
-        <v>0.8527149875534512</v>
-      </c>
-      <c r="N47">
-        <v>0.869104366587707</v>
-      </c>
-      <c r="O47">
         <v>0.8851051816225664</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.8986912103710879</v>
       </c>
     </row>
